--- a/BWI/bestwine_output/bestwine_Costa Rica.xlsx
+++ b/BWI/bestwine_output/bestwine_Costa Rica.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA68"/>
+  <dimension ref="A1:AA69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7761,6 +7761,99 @@
       <c r="Z68" s="2" t="inlineStr"/>
       <c r="AA68" s="2" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Vinos Y Licores Digitales, Sa</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>OLE Gourmet</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>118079</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Escazú</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>San José</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Del Cruce De San Rafael 600 Sur</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>https://olecr.com</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>leandro@olecr.com</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinosolegourmet/</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinosolegourmet</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>Leandro Aldaburu</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leandro-aldaburu-b83083229/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Costa Rica.xlsx
+++ b/BWI/bestwine_output/bestwine_Costa Rica.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA69"/>
+  <dimension ref="A1:AA70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7854,6 +7854,99 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Vinos Y Licores Digitales, Sa</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>OLE Gourmet</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>118079</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Escazú</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>San José</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Del Cruce De San Rafael 600 Sur</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://olecr.com</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>leandro@olecr.com</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinosolegourmet/</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinosolegourmet</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr"/>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>Leandro Aldaburu</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leandro-aldaburu-b83083229/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Costa Rica.xlsx
+++ b/BWI/bestwine_output/bestwine_Costa Rica.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA70"/>
+  <dimension ref="A1:AA71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -7947,6 +7947,99 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Vinos Y Licores Digitales, Sa</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>OLE Gourmet</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>118079</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Escazú</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>San José</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Del Cruce De San Rafael 600 Sur</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>https://olecr.com</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>leandro@olecr.com</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinosolegourmet/</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinosolegourmet</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr"/>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>Leandro Aldaburu</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leandro-aldaburu-b83083229/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Costa Rica.xlsx
+++ b/BWI/bestwine_output/bestwine_Costa Rica.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA71"/>
+  <dimension ref="A1:AA75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -8040,6 +8040,426 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Delika By Gourmet Imports Dcr S.a.</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Delika By Gourmet Imports Dcr S.a.</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>2957</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Alajuela Province</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Ofibodegas Del Oeste, Local 53 San Rafael</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delika.cr</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>info@delika.cr</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>+506 2277 1770</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>3101147086</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delikacr/</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/delikacr</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delikacr</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr"/>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>Alberto Perez Ibarra</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alberto-perez-ibarra-2b493a94/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Delika By Gourmet Imports Dcr S.a.</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Delika By Gourmet Imports Dcr S.a.</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>2957</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Alajuela Province</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Ofibodegas Del Oeste, Local 53 San Rafael</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delika.cr</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>info@delika.cr</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>+506 2277 1770</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>3101147086</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delikacr/</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/delikacr</t>
+        </is>
+      </c>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delikacr</t>
+        </is>
+      </c>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr"/>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>Raúl Bonilla</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/raulbonillach/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Delika By Gourmet Imports Dcr S.a.</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Delika By Gourmet Imports Dcr S.a.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>2957</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Alajuela Province</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Ofibodegas Del Oeste, Local 53 San Rafael</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delika.cr</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>info@delika.cr</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>+506 2277 1770</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>3101147086</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delikacr/</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/delikacr</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delikacr</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr"/>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>Paola Artavia</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paola-artavia-%F0%9F%87%A8%F0%9F%87%B7-59213657/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Delika By Gourmet Imports Dcr S.a.</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Delika By Gourmet Imports Dcr S.a.</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>2957</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>San Jose</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>Alajuela Province</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Ofibodegas Del Oeste, Local 53 San Rafael</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.delika.cr</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>info@delika.cr</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>+506 2277 1770</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>3101147086</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/delikacr/</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/delikacr</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delikacr</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>Jürgen F. Mormels</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>Ceo/ Owner</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/j%C3%BCrgen-f-mormels-b87b0a67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
